--- a/HCO+.xlsx
+++ b/HCO+.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -40,13 +40,13 @@
     <t xml:space="preserve">Intensity</t>
   </si>
   <si>
+    <t xml:space="preserve">Transition</t>
+  </si>
+  <si>
     <t xml:space="preserve">G001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2</t>
+    <t xml:space="preserve">45.3</t>
   </si>
   <si>
     <t xml:space="preserve">12.3</t>
@@ -55,6 +55,9 @@
     <t xml:space="preserve">2.0</t>
   </si>
   <si>
+    <t xml:space="preserve">J=9-0</t>
+  </si>
+  <si>
     <t xml:space="preserve">G007</t>
   </si>
   <si>
@@ -68,6 +71,165 @@
   </si>
   <si>
     <t xml:space="preserve">3.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G359,448-0,183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J=1-0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G359,952-0,007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G000,412-0,050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G000,692+0,005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Brick (G0,253)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSTTau042021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40 Blue Square</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40 Red Triangle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W40 Green Circle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr B2 (Main)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr B2 (North)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr B2 (South)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr A* (CND)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G0,013-0,021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G0,106-0,082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G0,145-0,086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Sickle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1,6-0,025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G359,948-0,052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G24 GMC 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G24 GMC 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G24 GMC 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G333,128-0,440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G333,163-0,101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G351,417+0,645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G0,489+0,010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G359,865-0,085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monoceros R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J=3-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G34,43+0,24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W3 (OH)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orion A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NGC 2264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7a (62")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sgr B2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRC + 10216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NML Cyg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J=2-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VY CMa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TX Cam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IK Tau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W Hya</t>
   </si>
 </sst>
 </file>
@@ -82,6 +244,7 @@
       <sz val="10"/>
       <name val="DejaVu Sans"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -102,6 +265,7 @@
       <sz val="10"/>
       <name val="DejaVu Serif"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -146,17 +310,33 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -282,10 +462,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr defaultColWidth="10.08203125" defaultRowHeight="13.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -304,45 +484,1221 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>670</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>359.448</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>-0.183</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>359.952</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>0.692</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>174.72</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>-15.46</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>160</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>502</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>502</v>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>502</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-0.028</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>64</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-0.041</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>359.944</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>-0.046</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>359.41</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>-0.021</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>-0.082</v>
+      </c>
+      <c r="D19" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>-0.086</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="D22" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>359.948</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>-0.052</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="6"/>
+    </row>
+    <row r="27" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.94</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>333.128</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-47.1</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>333.163</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>-0.101</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-91.5</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="5" t="n">
+        <v>351.417</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-13.6</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="6"/>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>359.865</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>-0.085</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G32" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>213.7</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>-12.6</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G33" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" s="6"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="5" t="n">
+        <v>34.43</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H34" s="6"/>
+    </row>
+    <row r="35" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="5" t="n">
+        <v>133.7</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>12300</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>-50.9</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="6"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>209</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>10900</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G37" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" s="5" t="n">
+        <v>203</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="6"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>203.1</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>11100</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>8.3</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>35.8</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>9800</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="G40" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="6"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>7600</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>86.7</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G41" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G42" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="5" t="n">
+        <v>221.45</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-25.9</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>83.32</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>-20.9</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>83.32</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G45" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>83.32</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B47" s="5" t="n">
+        <v>83.32</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G47" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>239.18</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="G48" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>239.18</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>-5.01</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>20.9</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G49" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="5" t="n">
+        <v>152.01</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>390</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="5" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>-28.75</v>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="G51" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="5" t="n">
+        <v>318</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>32.86</v>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>78</v>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>41.1</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
